--- a/Support Data/ADF_QC_LAB_RAW_MATERIAL_REPORT_RPT_ADF_LAB_RAW_MATERIAL_LAYOUT - 2026-08-14T093100.678 - 900 ROW.xlsx
+++ b/Support Data/ADF_QC_LAB_RAW_MATERIAL_REPORT_RPT_ADF_LAB_RAW_MATERIAL_LAYOUT - 2026-08-14T093100.678 - 900 ROW.xlsx
@@ -15150,7 +15150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:Q929"/>
+  <dimension ref="A2:R929"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.047619047619" style="1" customWidth="1"/>
@@ -20836,7 +20836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" ht="22.5" spans="1:17">
+    <row r="113" ht="22.5" spans="1:18">
       <c r="A113" s="4" t="s">
         <v>636</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" ht="33.75" spans="1:17">
+    <row r="114" ht="33.75" spans="1:18">
       <c r="A114" s="4" t="s">
         <v>640</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" ht="45" spans="1:17">
+    <row r="115" ht="45" spans="1:18">
       <c r="A115" s="4" t="s">
         <v>645</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" ht="56.25" spans="1:17">
+    <row r="116" ht="56.25" spans="1:18">
       <c r="A116" s="4" t="s">
         <v>653</v>
       </c>
@@ -21044,7 +21044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" ht="101.25" spans="1:17">
+    <row r="117" s="1" customFormat="1" ht="101.25" spans="1:18">
       <c r="A117" s="4" t="s">
         <v>386</v>
       </c>
@@ -21095,7 +21095,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="409.5" spans="1:17">
+    <row r="118" s="1" customFormat="1" ht="409.5" spans="1:18">
       <c r="A118" s="4" t="s">
         <v>398</v>
       </c>
@@ -21145,8 +21145,12 @@
       <c r="Q118" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="119" s="1" customFormat="1" ht="33.75" spans="1:17">
+      <c r="R118" s="1">
+        <f>LEN(I118)</f>
+        <v>791</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A119" s="4" t="s">
         <v>675</v>
       </c>
@@ -21191,7 +21195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="120" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A120" s="4" t="s">
         <v>682</v>
       </c>
@@ -21236,7 +21240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="121" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A121" s="4" t="s">
         <v>687</v>
       </c>
@@ -21281,7 +21285,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="122" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A122" s="4" t="s">
         <v>693</v>
       </c>
@@ -21326,7 +21330,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="1" ht="56.25" spans="1:17">
+    <row r="123" s="1" customFormat="1" ht="56.25" spans="1:18">
       <c r="A123" s="4" t="s">
         <v>416</v>
       </c>
@@ -21377,7 +21381,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="124" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A124" s="4" t="s">
         <v>425</v>
       </c>
@@ -21428,7 +21432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="125" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A125" s="4" t="s">
         <v>709</v>
       </c>
@@ -21473,7 +21477,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="126" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A126" s="4" t="s">
         <v>717</v>
       </c>
@@ -21524,7 +21528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" s="1" customFormat="1" ht="33.75" spans="1:17">
+    <row r="127" s="1" customFormat="1" ht="33.75" spans="1:18">
       <c r="A127" s="4" t="s">
         <v>722</v>
       </c>
@@ -21575,7 +21579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" s="1" customFormat="1" ht="56.25" spans="1:17">
+    <row r="128" s="1" customFormat="1" ht="56.25" spans="1:18">
       <c r="A128" s="4" t="s">
         <v>725</v>
       </c>

--- a/Support Data/ADF_QC_LAB_RAW_MATERIAL_REPORT_RPT_ADF_LAB_RAW_MATERIAL_LAYOUT - 2026-08-14T093100.678 - 900 ROW.xlsx
+++ b/Support Data/ADF_QC_LAB_RAW_MATERIAL_REPORT_RPT_ADF_LAB_RAW_MATERIAL_LAYOUT - 2026-08-14T093100.678 - 900 ROW.xlsx
@@ -15150,7 +15150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:R929"/>
+  <dimension ref="A2:Q929"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.047619047619" style="1" customWidth="1"/>
@@ -20836,7 +20836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" ht="22.5" spans="1:18">
+    <row r="113" ht="22.5" spans="1:17">
       <c r="A113" s="4" t="s">
         <v>636</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" ht="33.75" spans="1:18">
+    <row r="114" ht="33.75" spans="1:17">
       <c r="A114" s="4" t="s">
         <v>640</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" ht="45" spans="1:18">
+    <row r="115" ht="45" spans="1:17">
       <c r="A115" s="4" t="s">
         <v>645</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" ht="56.25" spans="1:18">
+    <row r="116" ht="56.25" spans="1:17">
       <c r="A116" s="4" t="s">
         <v>653</v>
       </c>
@@ -21044,7 +21044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" ht="101.25" spans="1:18">
+    <row r="117" s="1" customFormat="1" ht="101.25" spans="1:17">
       <c r="A117" s="4" t="s">
         <v>386</v>
       </c>
@@ -21095,7 +21095,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="409.5" spans="1:18">
+    <row r="118" s="1" customFormat="1" ht="409.5" spans="1:17">
       <c r="A118" s="4" t="s">
         <v>398</v>
       </c>
@@ -21145,12 +21145,8 @@
       <c r="Q118" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="R118" s="1">
-        <f>LEN(I118)</f>
-        <v>791</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="1" ht="33.75" spans="1:18">
+    </row>
+    <row r="119" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A119" s="4" t="s">
         <v>675</v>
       </c>
@@ -21195,7 +21191,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="120" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A120" s="4" t="s">
         <v>682</v>
       </c>
@@ -21240,7 +21236,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="121" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A121" s="4" t="s">
         <v>687</v>
       </c>
@@ -21285,7 +21281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="122" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A122" s="4" t="s">
         <v>693</v>
       </c>
@@ -21330,7 +21326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="1" ht="56.25" spans="1:18">
+    <row r="123" s="1" customFormat="1" ht="56.25" spans="1:17">
       <c r="A123" s="4" t="s">
         <v>416</v>
       </c>
@@ -21381,7 +21377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="124" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A124" s="4" t="s">
         <v>425</v>
       </c>
@@ -21432,7 +21428,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="125" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A125" s="4" t="s">
         <v>709</v>
       </c>
@@ -21477,7 +21473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="126" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A126" s="4" t="s">
         <v>717</v>
       </c>
@@ -21528,7 +21524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" s="1" customFormat="1" ht="33.75" spans="1:18">
+    <row r="127" s="1" customFormat="1" ht="33.75" spans="1:17">
       <c r="A127" s="4" t="s">
         <v>722</v>
       </c>
@@ -21579,7 +21575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" s="1" customFormat="1" ht="56.25" spans="1:18">
+    <row r="128" s="1" customFormat="1" ht="56.25" spans="1:17">
       <c r="A128" s="4" t="s">
         <v>725</v>
       </c>
